--- a/business_forms/048_market_entry_research_consulting_contact_form--business_forms.xlsx
+++ b/business_forms/048_market_entry_research_consulting_contact_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'work'}</t>
+          <t>work</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Work'}</t>
+          <t>Work</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'personal'}</t>
+          <t>personal</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Personal'}</t>
+          <t>Personal</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'software'}</t>
+          <t>software</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Software'}</t>
+          <t>Software</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'hardware'}</t>
+          <t>hardware</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Hardware'}</t>
+          <t>Hardware</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'service'}</t>
+          <t>service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Service'}</t>
+          <t>Service</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'planning'}</t>
+          <t>planning</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Planning'}</t>
+          <t>Planning</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'save_for_later'}</t>
+          <t>save_for_later</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Save for Later'}</t>
+          <t>Save for Later</t>
         </is>
       </c>
     </row>
